--- a/output/pdf_financials_xlsx/EAGL.xlsx
+++ b/output/pdf_financials_xlsx/EAGL.xlsx
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
@@ -4268,7 +4268,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4662,7 +4666,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EAGL.xlsx
+++ b/output/pdf_financials_xlsx/EAGL.xlsx
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.000761</v>
+        <v>0.128875</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.038639</v>
+        <v>0.310149</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.040533</v>
+        <v>0.269309</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000163</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>5.7e-05</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.127688</v>
+        <v>-0.127802</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.301371</v>
+        <v>-0.301534</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.274788</v>
+        <v>-0.274845</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.127688</v>
+        <v>-0.127802</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.301371</v>
+        <v>-0.301534</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.274788</v>
+        <v>-0.274845</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.320513</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.161924</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003195</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.320513</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.161924</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003195</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">

--- a/output/pdf_financials_xlsx/EAGL.xlsx
+++ b/output/pdf_financials_xlsx/EAGL.xlsx
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.002498</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.006256</v>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
@@ -4122,7 +4122,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
